--- a/output/pdf_financials_xlsx/TXG.xlsx
+++ b/output/pdf_financials_xlsx/TXG.xlsx
@@ -1309,10 +1309,10 @@
         <v>-77.16</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>113.951</v>
+        <v>-19.991</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>54.653</v>
+        <v>2.061</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-43.675</v>
@@ -1597,10 +1597,10 @@
         <v>-76.23699999999999</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>66.971</v>
+        <v>-66.971</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>26.296</v>
+        <v>-26.296</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-24.574</v>
@@ -1768,10 +1768,10 @@
         <v>-76.23699999999999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>66.971</v>
+        <v>-66.971</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.296</v>
+        <v>-26.296</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-24.574</v>
@@ -1939,10 +1939,10 @@
         <v>448.452941</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>608.827273</v>
+        <v>-608.827273</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>657.4</v>
+        <v>-657.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>79.270968</v>
@@ -1996,10 +1996,10 @@
         <v>-77.16</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>113.951</v>
+        <v>-19.991</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>54.653</v>
+        <v>2.061</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-43.675</v>
@@ -2110,10 +2110,10 @@
         <v>-76.52800000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>114.746</v>
+        <v>-19.196</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>55.597</v>
+        <v>3.005</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-42.491</v>
@@ -2254,10 +2254,10 @@
         <v>-1.196215655780197</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>41.22824722907215</v>
+        <v>-235.0057525886649</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>51.88553235869943</v>
+        <v>1375.885492479379</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-43.73440183171151</v>
@@ -3268,22 +3268,22 @@
         <v>3.263</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>39.5</v>
+        <v>9</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>43.6</v>
+        <v>12.2</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>55.6</v>
+        <v>21.8</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>48.1</v>
+        <v>17.5</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>65.7</v>
+        <v>16.5</v>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -61437,10 +61437,10 @@
         </is>
       </c>
       <c r="J559" s="5" t="n">
-        <v>26.296</v>
+        <v>-26.296</v>
       </c>
       <c r="K559" s="5" t="n">
-        <v>24.574</v>
+        <v>-24.574</v>
       </c>
       <c r="L559" t="inlineStr">
         <is>
@@ -64496,10 +64496,10 @@
         </is>
       </c>
       <c r="I591" s="5" t="n">
-        <v>66.971</v>
+        <v>-66.971</v>
       </c>
       <c r="J591" s="5" t="n">
-        <v>26.296</v>
+        <v>-26.296</v>
       </c>
       <c r="K591" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TXG.xlsx
+++ b/output/pdf_financials_xlsx/TXG.xlsx
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.080179</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.407</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.638</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-1.622</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-1.689</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-7.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="13">
@@ -1984,19 +1984,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.029286</v>
+        <v>-0.949107</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-17.755843</v>
+        <v>-17.348843</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-67.892</v>
+        <v>-67.254</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-77.16</v>
+        <v>-75.538</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-19.991</v>
+        <v>-18.302</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>2.061</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>350.7</v>
+        <v>358.5</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="28">
@@ -2098,19 +2098,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.029286</v>
+        <v>-0.949107</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-17.755843</v>
+        <v>-17.348843</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-67.553</v>
+        <v>-66.91500000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-76.52800000000001</v>
+        <v>-74.90600000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-19.196</v>
+        <v>-17.507</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>3.005</v>
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>542.3</v>
+        <v>550.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>676.3</v>
+        <v>682.3</v>
       </c>
     </row>
     <row r="30">
@@ -3268,22 +3268,22 @@
         <v>3.263</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>9</v>
+        <v>39.5</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>12.2</v>
+        <v>43.6</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>21.8</v>
+        <v>55.6</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>17.5</v>
+        <v>48.1</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>17.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>16.5</v>
+        <v>65.7</v>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
@@ -7838,10 +7838,10 @@
         <v>-164.4</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-40</v>
+        <v>-42.7</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="O124" s="1" t="inlineStr">
         <is>
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-8.6</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="125">
@@ -7895,10 +7895,10 @@
         <v>-164.4</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-40</v>
+        <v>-42.7</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="O125" s="1" t="inlineStr">
         <is>
@@ -7906,10 +7906,10 @@
         </is>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-8.6</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="126">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -23514,7 +23514,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -25508,7 +25512,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -45182,7 +45190,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -65708,7 +65716,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E604" s="5" t="n">
